--- a/results/MHD/node2vec_embedding_size_results.xlsx
+++ b/results/MHD/node2vec_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8451211401566198</v>
+        <v>0.8361259827252328</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8381129319050684</v>
+        <v>0.8379222885936116</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8512824268108252</v>
+        <v>0.8293447271261911</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8441978810946746</v>
+        <v>0.8238871565446196</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/node2vec_embedding_size_results.xlsx
+++ b/results/MHD/node2vec_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8361259827252328</v>
+        <v>0.8423660827470899</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8379222885936116</v>
+        <v>0.8353145245207626</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8293447271261911</v>
+        <v>0.8256260289635033</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8238871565446196</v>
+        <v>0.8197036982003665</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/node2vec_embedding_size_results.xlsx
+++ b/results/MHD/node2vec_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8423660827470899</v>
+        <v>0.8374719764187752</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8353145245207626</v>
+        <v>0.8311295271196435</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8256260289635033</v>
+        <v>0.8342771835153145</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8197036982003665</v>
+        <v>0.8271858027779697</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/node2vec_embedding_size_results.xlsx
+++ b/results/MHD/node2vec_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8374719764187752</v>
+        <v>0.8390914487451135</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8311295271196435</v>
+        <v>0.829955930504287</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8342771835153145</v>
+        <v>0.8308516942062265</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8271858027779697</v>
+        <v>0.8252540696496498</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/node2vec_embedding_size_results.xlsx
+++ b/results/MHD/node2vec_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8390914487451135</v>
+        <v>0.8399725955434534</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.829955930504287</v>
+        <v>0.8337796587209304</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8308516942062265</v>
+        <v>0.8318430915315718</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8252540696496498</v>
+        <v>0.8238940170075996</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/node2vec_embedding_size_results.xlsx
+++ b/results/MHD/node2vec_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8399725955434534</v>
+        <v>0.8383955575139268</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8337796587209304</v>
+        <v>0.8399204492418848</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8318430915315718</v>
+        <v>0.8320705212561188</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8238940170075996</v>
+        <v>0.8250973857836993</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/node2vec_embedding_size_results.xlsx
+++ b/results/MHD/node2vec_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8383955575139268</v>
+        <v>0.8417059473171795</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8399204492418848</v>
+        <v>0.8387180501508643</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8320705212561188</v>
+        <v>0.8275777789700266</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8250973857836993</v>
+        <v>0.8251985349406772</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/node2vec_embedding_size_results.xlsx
+++ b/results/MHD/node2vec_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8417059473171795</v>
+        <v>0.8430947789313826</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8387180501508643</v>
+        <v>0.8358356279960949</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8275777789700266</v>
+        <v>0.8301203344442921</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8251985349406772</v>
+        <v>0.830630754734808</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/node2vec_embedding_size_results.xlsx
+++ b/results/MHD/node2vec_embedding_size_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8430947789313826</v>
+        <v>0.8338728348346388</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8358356279960949</v>
+        <v>0.8373761661616749</v>
       </c>
     </row>
     <row r="4">
@@ -461,15 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8301203344442921</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.830630754734808</v>
+        <v>0.8275941566115392</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/node2vec_embedding_size_results.xlsx
+++ b/results/MHD/node2vec_embedding_size_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8338728348346388</v>
+        <v>0.8385766386817923</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8373761661616749</v>
+        <v>0.836007165278328</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,15 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8275941566115392</v>
+        <v>0.8271158487152317</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.8187854081354061</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/node2vec_embedding_size_results.xlsx
+++ b/results/MHD/node2vec_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8385766386817923</v>
+        <v>0.8381200439202336</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.836007165278328</v>
+        <v>0.8346898979840258</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8271158487152317</v>
+        <v>0.8261369110404722</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8187854081354061</v>
+        <v>0.8248362317165039</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/node2vec_embedding_size_results.xlsx
+++ b/results/MHD/node2vec_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8381200439202336</v>
+        <v>0.8338342357004563</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8346898979840258</v>
+        <v>0.8322792427232028</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8261369110404722</v>
+        <v>0.8322424858955635</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8248362317165039</v>
+        <v>0.8226780457909166</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/node2vec_embedding_size_results.xlsx
+++ b/results/MHD/node2vec_embedding_size_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8338342357004563</v>
+        <v>0.8498324579153106</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8322792427232028</v>
+        <v>0.8473706462778301</v>
       </c>
     </row>
     <row r="4">
@@ -461,15 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8322424858955635</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.8226780457909166</v>
+        <v>0.8431637515113868</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/node2vec_embedding_size_results.xlsx
+++ b/results/MHD/node2vec_embedding_size_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8498324579153106</v>
+        <v>0.8406525825802473</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8473706462778301</v>
+        <v>0.8399621251912045</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,15 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8431637515113868</v>
+        <v>0.8365871660444288</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.8361020603363662</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/node2vec_embedding_size_results.xlsx
+++ b/results/MHD/node2vec_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8406525825802473</v>
+        <v>0.8451211401566198</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8399621251912045</v>
+        <v>0.8381129319050684</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8365871660444288</v>
+        <v>0.8512824268108252</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8361020603363662</v>
+        <v>0.8441978810946746</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/node2vec_embedding_size_results.xlsx
+++ b/results/MHD/node2vec_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8451211401566198</v>
+        <v>0.8399646011011519</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8381129319050684</v>
+        <v>0.8307137803964505</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8512824268108252</v>
+        <v>0.8363928718575456</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8441978810946746</v>
+        <v>0.8375185357770208</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/node2vec_embedding_size_results.xlsx
+++ b/results/MHD/node2vec_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8399646011011519</v>
+        <v>0.8406525825802473</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8307137803964505</v>
+        <v>0.8399621251912045</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8363928718575456</v>
+        <v>0.8365871660444288</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8375185357770208</v>
+        <v>0.8361020603363662</v>
       </c>
     </row>
   </sheetData>
